--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132718137</v>
       </c>
       <c r="B2" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132718135</v>
       </c>
       <c r="B3" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B2" t="n">
         <v>93197</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R2" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B3" t="n">
         <v>93197</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R3" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R2" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R3" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132718137</v>
       </c>
       <c r="B2" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132718135</v>
       </c>
       <c r="B3" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B2" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R2" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B3" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R3" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B2" t="n">
         <v>93201</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R2" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B3" t="n">
         <v>93201</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R3" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B2" t="n">
         <v>93206</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R2" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B3" t="n">
         <v>93206</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R3" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B2" t="n">
         <v>93206</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R2" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B3" t="n">
         <v>93206</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R3" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132718137</v>
+        <v>132718135</v>
       </c>
       <c r="B2" t="n">
-        <v>93206</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607550</v>
+        <v>607473</v>
       </c>
       <c r="R2" t="n">
-        <v>6514767</v>
+        <v>6514681</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132718135</v>
+        <v>132718137</v>
       </c>
       <c r="B3" t="n">
-        <v>93206</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607473</v>
+        <v>607550</v>
       </c>
       <c r="R3" t="n">
-        <v>6514681</v>
+        <v>6514767</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +900,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132791902</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Enstaberga N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607502</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6514753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14862-2026 artfynd.xlsx
+++ b/artfynd/A 14862-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132791902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>